--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="186">
   <si>
     <t/>
   </si>
@@ -223,6 +223,15 @@
     <t>CADBURY OREO 58.5G</t>
   </si>
   <si>
+    <t>20141836</t>
+  </si>
+  <si>
+    <t>CADBURY CRISP-IT 52G</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
     <t>20057444</t>
   </si>
   <si>
@@ -241,124 +250,139 @@
     <t>KINDER/J CHOC BOYS20</t>
   </si>
   <si>
+    <t>20120946</t>
+  </si>
+  <si>
+    <t>KINDER JOY DC COMICS</t>
+  </si>
+  <si>
+    <t>20139949</t>
+  </si>
+  <si>
+    <t>LMNILO CRNCHY CHO 18</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20129814</t>
+  </si>
+  <si>
+    <t>MLKITA CNDY BTES 24G</t>
+  </si>
+  <si>
+    <t>20135665</t>
+  </si>
+  <si>
+    <t>JLO CHOCOEGG DRMON25</t>
+  </si>
+  <si>
+    <t>20135198</t>
+  </si>
+  <si>
+    <t>WONHAE YOG.GUM ORI48</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20139889</t>
+  </si>
+  <si>
+    <t>WNHAE PISTACHIO CHOC</t>
+  </si>
+  <si>
+    <t>20139890</t>
+  </si>
+  <si>
+    <t>WNHAE STRW CHEESCAKE</t>
+  </si>
+  <si>
+    <t>20141002</t>
+  </si>
+  <si>
+    <t>WONHAE MTCHA BRY 30G</t>
+  </si>
+  <si>
+    <t>20135661</t>
+  </si>
+  <si>
+    <t>WNHAE GMMY MXD.FRT32</t>
+  </si>
+  <si>
+    <t>20117108</t>
+  </si>
+  <si>
+    <t>BENG-BENG PCK 3X20G</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20044008</t>
+  </si>
+  <si>
+    <t>BENG-BENG MAXX 32G</t>
+  </si>
+  <si>
+    <t>20113490</t>
+  </si>
+  <si>
+    <t>BENG-BENG ALMOND 35G</t>
+  </si>
+  <si>
+    <t>10000322</t>
+  </si>
+  <si>
+    <t>CHOKI CHOKI CHO 4X9G</t>
+  </si>
+  <si>
+    <t>10000760</t>
+  </si>
+  <si>
+    <t>FISH.EXTRA STRG PT22</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>10001414</t>
+  </si>
+  <si>
+    <t>FISH.STRNG.MINT HJ22</t>
+  </si>
+  <si>
+    <t>10005583</t>
+  </si>
+  <si>
+    <t>FISHERMAN'S LEMON 22</t>
+  </si>
+  <si>
+    <t>20068396</t>
+  </si>
+  <si>
+    <t>FSHERMAN'S SPRMNT 22</t>
+  </si>
+  <si>
+    <t>20069699</t>
+  </si>
+  <si>
+    <t>FSHRMAN'S HNY&amp;LMN 22</t>
+  </si>
+  <si>
+    <t>20054913</t>
+  </si>
+  <si>
+    <t>FSHERMAN'S BLKCRN 22</t>
+  </si>
+  <si>
     <t>20132839</t>
   </si>
   <si>
     <t>KINDER CHOC CRMY 19G</t>
   </si>
   <si>
-    <t>20139949</t>
-  </si>
-  <si>
-    <t>LMNILO CRNCHY CHO 18</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20129814</t>
-  </si>
-  <si>
-    <t>MLKITA CNDY BTES 24G</t>
-  </si>
-  <si>
-    <t>20135198</t>
-  </si>
-  <si>
-    <t>WONHAE YOG.GUM ORI48</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20139889</t>
-  </si>
-  <si>
-    <t>WNHAE PISTACHIO CHOC</t>
-  </si>
-  <si>
-    <t>20139890</t>
-  </si>
-  <si>
-    <t>WNHAE STRW CHEESCAKE</t>
-  </si>
-  <si>
-    <t>20141002</t>
-  </si>
-  <si>
-    <t>WONHAE MTCHA BRY 30G</t>
-  </si>
-  <si>
-    <t>20135661</t>
-  </si>
-  <si>
-    <t>WNHAE GMMY MXD.FRT32</t>
-  </si>
-  <si>
-    <t>20117108</t>
-  </si>
-  <si>
-    <t>BENG-BENG PCK 3X20G</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20044008</t>
-  </si>
-  <si>
-    <t>BENG-BENG MAXX 32G</t>
-  </si>
-  <si>
-    <t>20113490</t>
-  </si>
-  <si>
-    <t>BENG-BENG ALMOND 35G</t>
-  </si>
-  <si>
-    <t>10000322</t>
-  </si>
-  <si>
-    <t>CHOKI CHOKI CHO 4X9G</t>
-  </si>
-  <si>
-    <t>10000760</t>
-  </si>
-  <si>
-    <t>FISH.EXTRA STRG PT22</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>10001414</t>
-  </si>
-  <si>
-    <t>FISH.STRNG.MINT HJ22</t>
-  </si>
-  <si>
-    <t>10005583</t>
-  </si>
-  <si>
-    <t>FISHERMAN'S LEMON 22</t>
-  </si>
-  <si>
-    <t>20068396</t>
-  </si>
-  <si>
-    <t>FSHERMAN'S SPRMNT 22</t>
-  </si>
-  <si>
-    <t>20069699</t>
-  </si>
-  <si>
-    <t>FSHRMAN'S HNY&amp;LMN 22</t>
-  </si>
-  <si>
-    <t>20054913</t>
-  </si>
-  <si>
-    <t>FSHERMAN'S BLKCRN 22</t>
+    <t>15</t>
   </si>
   <si>
     <t>20122072</t>
@@ -367,19 +391,10 @@
     <t>NUTELLA B-READY/F 22</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>10009988</t>
   </si>
   <si>
     <t>FERRERO RCHR CHO37.5</t>
-  </si>
-  <si>
-    <t>20135665</t>
-  </si>
-  <si>
-    <t>JLO CHOCOEGG DRMON25</t>
   </si>
   <si>
     <t>20137065</t>
@@ -946,7 +961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1568,70 +1583,70 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1648,10 +1663,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1659,19 +1674,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1688,10 +1703,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1708,10 +1723,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1719,19 +1734,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1739,19 +1754,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1759,19 +1774,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -1788,10 +1803,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -1808,10 +1823,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -1819,19 +1834,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="E44" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -1839,19 +1854,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -1868,10 +1883,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -1888,10 +1903,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -1899,19 +1914,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="E48" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -1919,19 +1934,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -1939,19 +1954,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -1959,22 +1974,22 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1988,13 +2003,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2008,70 +2023,70 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2088,10 +2103,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2108,10 +2123,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2119,19 +2134,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2139,19 +2154,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2159,19 +2174,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2179,19 +2194,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2208,10 +2223,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2228,10 +2243,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2239,19 +2254,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="E65" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2259,19 +2274,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2288,10 +2303,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2308,13 +2323,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>156</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2328,10 +2343,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2348,13 +2363,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2368,13 +2383,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>156</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2388,73 +2403,73 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>161</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2468,13 +2483,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2488,10 +2503,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2499,19 +2514,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2519,21 +2534,61 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F81" s="1" t="s">
         <v>5</v>
       </c>
     </row>
